--- a/reports/feature_importance.xlsx
+++ b/reports/feature_importance.xlsx
@@ -456,7 +456,7 @@
         <v>2.802490788687054</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7225815936650115</v>
+        <v>0.7225815936650116</v>
       </c>
     </row>
     <row r="4">
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.130899270583264</v>
+        <v>0.1308992705832641</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08368488491980677</v>
+        <v>0.08368488491980679</v>
       </c>
     </row>
     <row r="6">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1208323033961412</v>
+        <v>0.1208323033961413</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1564808197875412</v>
+        <v>0.1564808197875413</v>
       </c>
     </row>
     <row r="7">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0557941507541256</v>
+        <v>0.05579415075412544</v>
       </c>
       <c r="C7" t="n">
         <v>0.1181174583394983</v>
@@ -521,7 +521,7 @@
         <v>0.01455752067386573</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05409666863991543</v>
+        <v>0.05409666863991562</v>
       </c>
     </row>
     <row r="9">
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009627835302730148</v>
+        <v>0.009627835302730193</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0839793822636983</v>
+        <v>0.08397938226369832</v>
       </c>
     </row>
     <row r="10">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003335877249216838</v>
+        <v>0.003335877249216779</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006205995769826936</v>
+        <v>0.006205995769826935</v>
       </c>
     </row>
   </sheetData>
